--- a/data/codes_valides.xlsx
+++ b/data/codes_valides.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,15 +461,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>note_par</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>removed</t>
         </is>
@@ -508,15 +503,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>2024-05-14</t>
         </is>
       </c>
-      <c r="I2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -553,15 +543,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>2024-05-14</t>
         </is>
       </c>
-      <c r="I3" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -598,15 +583,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dr Bianchi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>2024-05-03</t>
         </is>
       </c>
-      <c r="I4" t="b">
+      <c r="H4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -643,15 +623,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dr Perrot</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="I5" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -688,15 +663,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
           <t>2024-04-16</t>
         </is>
       </c>
-      <c r="I6" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -733,15 +703,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
           <t>2023-03-09</t>
         </is>
       </c>
-      <c r="I7" t="b">
+      <c r="H7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -778,15 +743,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="I8" t="b">
+      <c r="H8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/codes_valides.xlsx
+++ b/data/codes_valides.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000077</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
